--- a/output/pdf_financials_xlsx/AIS.xlsx
+++ b/output/pdf_financials_xlsx/AIS.xlsx
@@ -5004,34 +5004,34 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.144697</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.311812</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.572201</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.642958</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.703232</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.148977</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.286219</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.397395</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.55852</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.55852</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>0</v>
@@ -9978,7 +9978,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -10982,7 +10986,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -12492,7 +12500,11 @@
           <t>Reserves 17</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -13882,7 +13894,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -14228,7 +14244,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -14662,7 +14682,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -15276,7 +15300,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AIS.xlsx
+++ b/output/pdf_financials_xlsx/AIS.xlsx
@@ -2077,46 +2077,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.269434</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.036592</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.24472</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.037645</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.360039</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.95904</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.073349</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.003372</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.454361</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.167501</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.241866</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.004904</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.016647</v>
       </c>
     </row>
     <row r="35">
@@ -2175,46 +2175,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.066287</v>
+        <v>0.335721</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.100526</v>
+        <v>0.137118</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.074762</v>
+        <v>0.319482</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.123885</v>
+        <v>0.16153</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.000794</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.360039</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.95904</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.073349</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.003372</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.11127</v>
+        <v>0.565631</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.524545</v>
+        <v>0.6920460000000001</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.2647</v>
+        <v>0.506566</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.05866</v>
+        <v>0.063564</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.028184</v>
+        <v>0.044831</v>
       </c>
     </row>
     <row r="37">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.6135890000000001</v>
+        <v>0.344155</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.526066</v>
+        <v>0.489474</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.360796</v>
+        <v>0.116076</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -2778,31 +2778,31 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.386902</v>
+        <v>0.026863</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.145571</v>
+        <v>0.186531</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.121466</v>
+        <v>0.048117</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.09303599999999999</v>
+        <v>0.08966399999999999</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.511433</v>
+        <v>0.057072</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.22863</v>
+        <v>0.061129</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.31735</v>
+        <v>0.075484</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.035509</v>
+        <v>0.030605</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.056406</v>
+        <v>0.039759</v>
       </c>
     </row>
     <row r="49">
@@ -6701,13 +6701,13 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.033025</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.040407</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009426</v>
       </c>
       <c r="M124" s="3" t="n">
         <v>0</v>
@@ -6756,13 +6756,13 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.033025</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.040407</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009426</v>
       </c>
       <c r="M125" s="3" t="n">
         <v>0</v>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -12590,7 +12590,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
@@ -20672,7 +20672,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -22034,7 +22038,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -23308,7 +23316,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -44100,7 +44112,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">

--- a/output/pdf_financials_xlsx/AIS.xlsx
+++ b/output/pdf_financials_xlsx/AIS.xlsx
@@ -719,25 +719,25 @@
         <v>0.281303</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.327514</v>
+        <v>0.357514</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.141199</v>
+        <v>0.171199</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.147237</v>
+        <v>0.177237</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.187614</v>
+        <v>0.217614</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.18666</v>
+        <v>0.21666</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.226392</v>
+        <v>0.232642</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.303103</v>
+        <v>0.330926</v>
       </c>
     </row>
     <row r="8">
@@ -872,7 +872,7 @@
         <v>1.421824</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.45913</v>
+        <v>0.48913</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>1.777873</v>
@@ -923,7 +923,7 @@
         <v>-1.421824</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.45913</v>
+        <v>-0.48913</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>-1.777873</v>
@@ -2395,10 +2395,10 @@
         <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.004275</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.001425</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>0</v>
@@ -2444,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.17949</v>
+        <v>0.183765</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0.001425</v>
+        <v>0.00285</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>0.013275</v>
@@ -2787,10 +2787,10 @@
         <v>0.048117</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.08966399999999999</v>
+        <v>0.08538900000000001</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.057072</v>
+        <v>0.055647</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.061129</v>
@@ -3905,10 +3905,10 @@
         <v>0</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.035971</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.008975</v>
       </c>
       <c r="L70" s="3" t="n">
         <v>0</v>
@@ -3954,10 +3954,10 @@
         <v>0.462649</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.658222</v>
+        <v>0.6941929999999999</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.446251</v>
+        <v>0.455226</v>
       </c>
       <c r="L71" s="3" t="n">
         <v>0.515952</v>
@@ -4150,10 +4150,10 @@
         <v>0.273243</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.159665</v>
+        <v>0.123694</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.207916</v>
+        <v>0.198941</v>
       </c>
       <c r="L75" s="3" t="n">
         <v>0.302349</v>
@@ -4413,10 +4413,10 @@
         <v>0.1460075457645412</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>17.06299253421817</v>
+        <v>17.99546350062215</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.2510767440722109</v>
+        <v>0.256126399485976</v>
       </c>
       <c r="L80" s="3" t="n">
         <v>0.1041137641515069</v>
@@ -5971,10 +5971,10 @@
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006796</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001702</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -6114,18 +6114,14 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>-0.001464</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>-0.001263</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-0.001703</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>0.000641</v>
@@ -6146,16 +6142,16 @@
         <v>0</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-0.047671</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-0.293619</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-0.134</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="O114" s="3" t="n">
         <v>0</v>
@@ -6167,10 +6163,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0.204396</v>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
@@ -6201,19 +6195,19 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.12858</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.43683</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.213259</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.11515</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.028285</v>
       </c>
     </row>
     <row r="116">
@@ -7063,25 +7057,17 @@
       <c r="J130" s="3" t="n">
         <v>0.073349</v>
       </c>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K130" s="3" t="n">
+        <v>0.003372</v>
+      </c>
+      <c r="L130" s="3" t="n">
+        <v>0.454361</v>
+      </c>
+      <c r="M130" s="3" t="n">
+        <v>0.167501</v>
+      </c>
+      <c r="N130" s="3" t="n">
+        <v>0.241866</v>
       </c>
       <c r="O130" s="1" t="inlineStr">
         <is>
@@ -7238,25 +7224,17 @@
       <c r="J133" s="3" t="n">
         <v>0.003372</v>
       </c>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K133" s="3" t="n">
+        <v>0.454361</v>
+      </c>
+      <c r="L133" s="3" t="n">
+        <v>0.167501</v>
+      </c>
+      <c r="M133" s="3" t="n">
+        <v>0.241866</v>
+      </c>
+      <c r="N133" s="3" t="n">
+        <v>0.004904</v>
       </c>
       <c r="O133" s="1" t="inlineStr">
         <is>
@@ -7292,10 +7270,10 @@
         </is>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006796</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001702</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -7356,7 +7334,7 @@
         </is>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-1.352857</v>
+        <v>-1.354559</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-1.141556</v>
@@ -12156,7 +12134,11 @@
           <t>Lease liabilities 14</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -12942,7 +12924,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -18316,7 +18302,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -18398,7 +18388,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -19738,7 +19732,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -19820,7 +19818,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -21614,7 +21616,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -21698,7 +21704,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -22298,7 +22308,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -22382,7 +22396,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -23576,7 +23594,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -23660,7 +23682,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -25376,7 +25402,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -25462,7 +25492,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -26570,7 +26604,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -27908,7 +27946,11 @@
           <t>Sale (purchase) of marketable securities</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -28854,7 +28896,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -30140,7 +30186,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E269" s="5" t="n">
         <v>-0.001464</v>
       </c>
@@ -30224,7 +30274,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E270" s="5" t="n">
         <v>0.204396</v>
       </c>
@@ -30966,7 +31020,11 @@
           <t>Directors’ fees 9</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -32874,7 +32932,11 @@
           <t>Directors’ fees 10</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -34216,7 +34278,11 @@
           <t>Directors’ fees 11</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -37704,7 +37770,11 @@
           <t>Directors’ fees 13</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -38904,7 +38974,11 @@
           <t>Directors fees 11</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
